--- a/fhir/core/StructureDefinition-dk-core-minimaldocumentreference.xlsx
+++ b/fhir/core/StructureDefinition-dk-core-minimaldocumentreference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.5.0</t>
+    <t>3.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-19T17:27:08+01:00</t>
+    <t>2026-03-11T23:16:27+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/core/StructureDefinition-dk-core-minimaldocumentreference.xlsx
+++ b/fhir/core/StructureDefinition-dk-core-minimaldocumentreference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3067" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3068" uniqueCount="589">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.6.0</t>
+    <t>3.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T23:16:27+01:00</t>
+    <t>2026-05-30T15:25:27+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -651,7 +651,13 @@
     <t>Specifies the version of the DocumentReference profile for a standard.</t>
   </si>
   <si>
-    <t>Optional Extension Element - found in all resources.</t>
+    <t>R5: `DocumentReference.version` (new:string)</t>
+  </si>
+  <si>
+    <t>Element `DocumentReference.version` has a context of DocumentReference based on following the parent source element upwards and mapping to `DocumentReference`.
+Element `DocumentReference.version` has a context of Media based on following the parent source element upwards and mapping to `Media`.
+Element `DocumentReference.version` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).
+While each resource, including the DocumentReference itself, has its own version identifier, this is a formal identifier for the logical version of the DocumentReference as a whole. It would remain constant if the resources were moved to a new server, and all got new individual resource versions, for example.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -4384,7 +4390,9 @@
       <c r="M18" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="N18" s="2"/>
+      <c r="N18" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>81</v>
@@ -4442,7 +4450,7 @@
         <v>83</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>124</v>
@@ -4457,7 +4465,7 @@
         <v>81</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>195</v>
+        <v>81</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>81</v>
@@ -4474,10 +4482,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4557,7 +4565,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4598,10 +4606,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4624,19 +4632,19 @@
         <v>96</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -4685,7 +4693,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4700,36 +4708,36 @@
         <v>107</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AO20" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AP20" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AQ20" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AR20" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AR20" t="s" s="2">
-        <v>214</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4752,13 +4760,13 @@
         <v>96</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4797,7 +4805,7 @@
         <v>81</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
@@ -4807,7 +4815,7 @@
         <v>122</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4822,39 +4830,39 @@
         <v>107</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN21" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AO21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP21" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AQ21" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AR21" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AR21" t="s" s="2">
-        <v>226</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>81</v>
@@ -4876,13 +4884,13 @@
         <v>96</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4933,7 +4941,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -4951,33 +4959,33 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN22" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AO22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP22" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AQ22" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AR22" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AR22" t="s" s="2">
-        <v>226</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5003,13 +5011,13 @@
         <v>172</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5035,11 +5043,11 @@
         <v>81</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>81</v>
@@ -5057,7 +5065,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>95</v>
@@ -5072,36 +5080,36 @@
         <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP23" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AR23" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AR23" t="s" s="2">
-        <v>238</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5127,13 +5135,13 @@
         <v>172</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5159,13 +5167,13 @@
         <v>81</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -5183,7 +5191,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5204,19 +5212,19 @@
         <v>81</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>81</v>
@@ -5224,10 +5232,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5250,16 +5258,16 @@
         <v>96</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5288,10 +5296,10 @@
         <v>176</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
@@ -5309,7 +5317,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5324,40 +5332,40 @@
         <v>107</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5376,16 +5384,16 @@
         <v>96</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5414,10 +5422,10 @@
         <v>162</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -5435,7 +5443,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5450,36 +5458,36 @@
         <v>107</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5502,13 +5510,13 @@
         <v>96</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5559,7 +5567,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5574,40 +5582,40 @@
         <v>107</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AP27" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AQ27" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AR27" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AQ27" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AR27" t="s" s="2">
-        <v>283</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5629,13 +5637,13 @@
         <v>131</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5685,7 +5693,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5703,19 +5711,19 @@
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>81</v>
@@ -5726,10 +5734,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5752,16 +5760,16 @@
         <v>96</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5811,7 +5819,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5826,36 +5834,36 @@
         <v>107</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AO29" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AP29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ29" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AR29" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ29" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AR29" t="s" s="2">
-        <v>304</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5878,16 +5886,16 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5937,7 +5945,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5952,36 +5960,36 @@
         <v>107</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AP30" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AQ30" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AR30" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="AR30" t="s" s="2">
-        <v>315</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6004,16 +6012,16 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6063,7 +6071,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6078,16 +6086,16 @@
         <v>107</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>81</v>
@@ -6104,10 +6112,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6130,16 +6138,16 @@
         <v>96</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6189,7 +6197,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6204,36 +6212,36 @@
         <v>107</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR32" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR32" t="s" s="2">
-        <v>334</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6354,10 +6362,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6480,14 +6488,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6509,16 +6517,16 @@
         <v>116</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>119</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6567,7 +6575,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6608,10 +6616,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6637,13 +6645,13 @@
         <v>172</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6669,13 +6677,13 @@
         <v>81</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -6693,7 +6701,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>95</v>
@@ -6708,16 +6716,16 @@
         <v>107</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -6729,15 +6737,15 @@
         <v>81</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6760,13 +6768,13 @@
         <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6817,7 +6825,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>95</v>
@@ -6832,16 +6840,16 @@
         <v>107</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>81</v>
@@ -6853,15 +6861,15 @@
         <v>81</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6887,16 +6895,16 @@
         <v>109</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6945,7 +6953,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6960,7 +6968,7 @@
         <v>107</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>81</v>
@@ -6969,27 +6977,27 @@
         <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ38" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AR38" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ38" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="AR38" t="s" s="2">
-        <v>368</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7012,19 +7020,19 @@
         <v>96</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -7073,7 +7081,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7088,36 +7096,36 @@
         <v>107</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AP39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ39" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AR39" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ39" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AR39" t="s" s="2">
-        <v>376</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7140,13 +7148,13 @@
         <v>96</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7197,7 +7205,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>95</v>
@@ -7218,10 +7226,10 @@
         <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>81</v>
@@ -7238,10 +7246,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7362,10 +7370,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7488,14 +7496,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7517,16 +7525,16 @@
         <v>116</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>119</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -7575,7 +7583,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7616,10 +7624,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7642,13 +7650,13 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7699,7 +7707,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>95</v>
@@ -7720,30 +7728,30 @@
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7864,10 +7872,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7990,10 +7998,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8019,14 +8027,14 @@
         <v>172</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -8039,7 +8047,7 @@
         <v>81</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>81</v>
@@ -8051,13 +8059,13 @@
         <v>81</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>81</v>
@@ -8075,7 +8083,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8090,7 +8098,7 @@
         <v>107</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>81</v>
@@ -8099,7 +8107,7 @@
         <v>81</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>81</v>
@@ -8108,7 +8116,7 @@
         <v>81</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>81</v>
@@ -8116,10 +8124,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8145,14 +8153,14 @@
         <v>172</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8165,7 +8173,7 @@
         <v>81</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>81</v>
@@ -8201,7 +8209,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8216,7 +8224,7 @@
         <v>107</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>81</v>
@@ -8225,7 +8233,7 @@
         <v>81</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>81</v>
@@ -8242,10 +8250,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8268,19 +8276,19 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>81</v>
@@ -8329,7 +8337,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8353,7 +8361,7 @@
         <v>81</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>81</v>
@@ -8362,7 +8370,7 @@
         <v>81</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>81</v>
@@ -8370,10 +8378,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8396,19 +8404,19 @@
         <v>96</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -8421,7 +8429,7 @@
         <v>81</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>81</v>
@@ -8457,7 +8465,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8472,7 +8480,7 @@
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>81</v>
@@ -8481,7 +8489,7 @@
         <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>81</v>
@@ -8490,7 +8498,7 @@
         <v>81</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>81</v>
@@ -8498,10 +8506,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8524,19 +8532,19 @@
         <v>96</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -8585,7 +8593,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8600,7 +8608,7 @@
         <v>107</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>81</v>
@@ -8609,7 +8617,7 @@
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>81</v>
@@ -8626,10 +8634,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8652,19 +8660,19 @@
         <v>96</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -8713,7 +8721,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8728,7 +8736,7 @@
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>81</v>
@@ -8737,7 +8745,7 @@
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>81</v>
@@ -8754,10 +8762,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8783,14 +8791,14 @@
         <v>109</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8803,7 +8811,7 @@
         <v>81</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>81</v>
@@ -8839,7 +8847,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8854,7 +8862,7 @@
         <v>107</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>81</v>
@@ -8863,7 +8871,7 @@
         <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>81</v>
@@ -8880,10 +8888,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8906,17 +8914,17 @@
         <v>96</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -8965,7 +8973,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8980,7 +8988,7 @@
         <v>107</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>81</v>
@@ -8989,7 +8997,7 @@
         <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>81</v>
@@ -9006,10 +9014,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9035,13 +9043,13 @@
         <v>150</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9071,7 +9079,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -9089,7 +9097,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9104,36 +9112,36 @@
         <v>107</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR55" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR55" t="s" s="2">
-        <v>475</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9156,16 +9164,16 @@
         <v>96</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9215,7 +9223,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9239,7 +9247,7 @@
         <v>81</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -9256,10 +9264,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9380,10 +9388,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9506,14 +9514,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9535,16 +9543,16 @@
         <v>116</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>119</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
@@ -9593,7 +9601,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9634,10 +9642,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9660,13 +9668,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9717,7 +9725,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9732,22 +9740,22 @@
         <v>107</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>81</v>
@@ -9758,10 +9766,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9784,16 +9792,16 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9823,7 +9831,7 @@
       </c>
       <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -9841,7 +9849,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9856,36 +9864,36 @@
         <v>107</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR61" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR61" t="s" s="2">
-        <v>500</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9908,13 +9916,13 @@
         <v>96</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9965,7 +9973,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -9986,13 +9994,13 @@
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>81</v>
@@ -10001,15 +10009,15 @@
         <v>81</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10130,10 +10138,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10256,10 +10264,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10282,16 +10290,16 @@
         <v>96</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10341,7 +10349,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10350,13 +10358,13 @@
         <v>95</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>81</v>
@@ -10365,7 +10373,7 @@
         <v>81</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>81</v>
@@ -10374,7 +10382,7 @@
         <v>81</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>81</v>
@@ -10382,10 +10390,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10408,23 +10416,23 @@
         <v>96</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q66" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="R66" t="s" s="2">
         <v>81</v>
@@ -10469,7 +10477,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10478,13 +10486,13 @@
         <v>95</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>81</v>
@@ -10493,7 +10501,7 @@
         <v>81</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>81</v>
@@ -10502,7 +10510,7 @@
         <v>81</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>81</v>
@@ -10510,10 +10518,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10536,13 +10544,13 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10573,7 +10581,7 @@
       </c>
       <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
@@ -10591,7 +10599,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10606,36 +10614,36 @@
         <v>107</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AQ67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR67" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR67" t="s" s="2">
-        <v>535</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10658,19 +10666,19 @@
         <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -10699,7 +10707,7 @@
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>81</v>
@@ -10717,7 +10725,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10732,20 +10740,20 @@
         <v>107</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN68" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="AO68" t="s" s="2">
-        <v>536</v>
-      </c>
       <c r="AP68" t="s" s="2">
         <v>81</v>
       </c>
@@ -10753,15 +10761,15 @@
         <v>81</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10784,13 +10792,13 @@
         <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10841,7 +10849,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10862,13 +10870,13 @@
         <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>81</v>
@@ -10877,15 +10885,15 @@
         <v>81</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11006,10 +11014,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11132,10 +11140,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11161,13 +11169,13 @@
         <v>109</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11217,7 +11225,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11226,13 +11234,13 @@
         <v>95</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>81</v>
@@ -11258,10 +11266,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11287,13 +11295,13 @@
         <v>137</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11322,10 +11330,10 @@
         <v>154</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>81</v>
@@ -11343,7 +11351,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11384,10 +11392,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11410,16 +11418,16 @@
         <v>96</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11469,7 +11477,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -11484,7 +11492,7 @@
         <v>107</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>81</v>
@@ -11493,7 +11501,7 @@
         <v>81</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>81</v>
@@ -11510,10 +11518,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11539,13 +11547,13 @@
         <v>109</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11595,7 +11603,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -11636,10 +11644,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11662,16 +11670,16 @@
         <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11721,7 +11729,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -11736,19 +11744,19 @@
         <v>107</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>81</v>
@@ -11757,7 +11765,7 @@
         <v>81</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
   </sheetData>
